--- a/Result/profitability/6803.xlsx
+++ b/Result/profitability/6803.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM73"/>
+  <dimension ref="A1:AM74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>3.51</v>
       </c>
       <c r="M2" t="n">
-        <v>4.39875</v>
+        <v>4.34</v>
       </c>
       <c r="N2" t="n">
-        <v>19.585</v>
+        <v>19.25625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>3.19</v>
       </c>
       <c r="M3" t="n">
-        <v>4.186249999999999</v>
+        <v>4.26375</v>
       </c>
       <c r="N3" t="n">
-        <v>20.3925</v>
+        <v>20.8</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.98</v>
       </c>
       <c r="M4" t="n">
-        <v>3.83375</v>
+        <v>3.82125</v>
       </c>
       <c r="N4" t="n">
-        <v>20.9275</v>
+        <v>20.70125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.69</v>
       </c>
       <c r="M5" t="n">
-        <v>3.48</v>
+        <v>3.48875</v>
       </c>
       <c r="N5" t="n">
-        <v>21.32625</v>
+        <v>21.20375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>2.39</v>
       </c>
       <c r="M6" t="n">
-        <v>3.235</v>
+        <v>3.115</v>
       </c>
       <c r="N6" t="n">
-        <v>21.86</v>
+        <v>21.61125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>2.27</v>
       </c>
       <c r="M7" t="n">
-        <v>2.84625</v>
+        <v>2.87375</v>
       </c>
       <c r="N7" t="n">
-        <v>22.3025</v>
+        <v>22.66375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.8</v>
       </c>
       <c r="M8" t="n">
-        <v>2.42125</v>
+        <v>2.40625</v>
       </c>
       <c r="N8" t="n">
-        <v>22.96125</v>
+        <v>22.82625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9699,6 +9699,133 @@
       </c>
       <c r="AM73" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>6803</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>2412</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1960</v>
+      </c>
+      <c r="E74" t="n">
+        <v>452</v>
+      </c>
+      <c r="F74" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="G74" t="n">
+        <v>412</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>17.10%</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>15</v>
+      </c>
+      <c r="J74" t="n">
+        <v>427</v>
+      </c>
+      <c r="K74" t="n">
+        <v>322</v>
+      </c>
+      <c r="L74" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="M74" t="n">
+        <v>4.5125</v>
+      </c>
+      <c r="N74" t="n">
+        <v>19.0325</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
+      </c>
+      <c r="V74" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W74" t="n">
+        <v>-0.1200000000000001</v>
+      </c>
+      <c r="X74" t="n">
+        <v>-0.02643171806167399</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>-1.080000000000002</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>-0.05449041372351171</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0.07000000000000028</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0.01609195402298846</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>-0.9800000000000004</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>-0.0496957403651116</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK74" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
